--- a/EXCEL/ASSIGNMENT_2.xlsx
+++ b/EXCEL/ASSIGNMENT_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EXCEL_NEW\ASSIGNMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56020D3-70E1-4323-8591-91079F489638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C85FC81-3064-4EF6-84D3-28A6967A5ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3276" yWindow="3276" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,17 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Dataset" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="142">
   <si>
     <t>Perform the following in the dataset from the 'Dataset' sheet.</t>
   </si>
@@ -452,6 +461,9 @@
   </si>
   <si>
     <t>this appears twice</t>
+  </si>
+  <si>
+    <t>Product Brand</t>
   </si>
 </sst>
 </file>
@@ -2040,6 +2052,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2061,6 +2074,9 @@
       <c r="F1" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="G1" s="9" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2081,6 +2097,10 @@
       <c r="F2" s="10" t="s">
         <v>28</v>
       </c>
+      <c r="G2" t="str">
+        <f>_xlfn.CONCAT(B2," ",C2)</f>
+        <v>Laptop Dell</v>
+      </c>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -2100,6 +2120,10 @@
       </c>
       <c r="F3" s="11" t="s">
         <v>32</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G32" si="0">_xlfn.CONCAT(B3," ",C3)</f>
+        <v>Sneakers Nike</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="6"/>
@@ -2129,6 +2153,10 @@
       <c r="F4" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>Coffee Maker Keurig</v>
+      </c>
       <c r="I4" s="6"/>
       <c r="J4" s="7"/>
       <c r="K4" s="6"/>
@@ -2157,6 +2185,10 @@
       <c r="F5" s="11" t="s">
         <v>28</v>
       </c>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>Smartphone Samsung</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7"/>
       <c r="K5" s="6"/>
@@ -2183,6 +2215,10 @@
         <v>20</v>
       </c>
       <c r="F6" s="10"/>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>Backpack North Face</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
@@ -2201,6 +2237,10 @@
       <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>Headphones Sony</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
@@ -2221,6 +2261,10 @@
       <c r="F8" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>T-shirt Adidas</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -2241,6 +2285,10 @@
       <c r="F9" s="11" t="s">
         <v>36</v>
       </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>Blender Ninja</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
@@ -2261,6 +2309,10 @@
       <c r="F10" s="10" t="s">
         <v>28</v>
       </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>Tablet Apple</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
@@ -2281,6 +2333,10 @@
       <c r="F11" s="11" t="s">
         <v>58</v>
       </c>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>Hiking Boots Timberland</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
@@ -2301,6 +2357,10 @@
       <c r="F12" s="10" t="s">
         <v>28</v>
       </c>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>Laptop HP</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
@@ -2319,6 +2379,10 @@
         <v>40</v>
       </c>
       <c r="F13" s="11"/>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sneakers Adidas</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -2337,6 +2401,10 @@
         <v>35</v>
       </c>
       <c r="F14" s="10"/>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>Coffee Maker Nespresso</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
@@ -2357,6 +2425,10 @@
       <c r="F15" s="11" t="s">
         <v>28</v>
       </c>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>Smartwatch Fitbit</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
@@ -2377,8 +2449,12 @@
       <c r="F16" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>Headphones Bose</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>71</v>
       </c>
@@ -2397,8 +2473,12 @@
       <c r="F17" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>Laptop Bag Samsonite</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>75</v>
       </c>
@@ -2417,8 +2497,12 @@
       <c r="F18" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>Smartwatch Huawei</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>77</v>
       </c>
@@ -2437,8 +2521,12 @@
       <c r="F19" s="11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>Laptop Asus</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>79</v>
       </c>
@@ -2457,8 +2545,12 @@
       <c r="F20" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunglasses Oakley</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>82</v>
       </c>
@@ -2475,8 +2567,12 @@
       <c r="F21" s="11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v>Camping Tent Coleman</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>85</v>
       </c>
@@ -2495,8 +2591,12 @@
       <c r="F22" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v>Camera Nikon</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>88</v>
       </c>
@@ -2515,8 +2615,12 @@
       <c r="F23" s="11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v>Microwave Panasonic</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>91</v>
       </c>
@@ -2533,8 +2637,12 @@
         <v>30</v>
       </c>
       <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24" t="str">
+        <f t="shared" si="0"/>
+        <v>Fitness Tracker Xiaomi</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>94</v>
       </c>
@@ -2553,8 +2661,12 @@
       <c r="F25" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G25" t="str">
+        <f t="shared" si="0"/>
+        <v>Smartphone Google</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>97</v>
       </c>
@@ -2571,8 +2683,12 @@
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G26" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunglasses Ray-Ban</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>99</v>
       </c>
@@ -2591,8 +2707,12 @@
       <c r="F27" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G27" t="str">
+        <f t="shared" si="0"/>
+        <v>Blender Vitamix</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>101</v>
       </c>
@@ -2611,8 +2731,12 @@
       <c r="F28" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" t="str">
+        <f t="shared" si="0"/>
+        <v>Dress Zara</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>104</v>
       </c>
@@ -2631,8 +2755,12 @@
       <c r="F29" s="11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G29" t="str">
+        <f t="shared" si="0"/>
+        <v>Toaster Hamilton</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>107</v>
       </c>
@@ -2651,8 +2779,12 @@
       <c r="F30" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G30" t="str">
+        <f t="shared" si="0"/>
+        <v>Fitness Tracker Garmin</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>109</v>
       </c>
@@ -2671,8 +2803,12 @@
       <c r="F31" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G31" t="str">
+        <f t="shared" si="0"/>
+        <v>Jeans Levi's</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>112</v>
       </c>
@@ -2690,6 +2826,10 @@
       </c>
       <c r="F32" s="11" t="s">
         <v>74</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="0"/>
+        <v>Watch Casio</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/EXCEL/ASSIGNMENT_2.xlsx
+++ b/EXCEL/ASSIGNMENT_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EXCEL_NEW\ASSIGNMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C85FC81-3064-4EF6-84D3-28A6967A5ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB7ABF5-B595-4572-A84B-8EEF1A1C7704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3276" yWindow="3276" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -470,6 +470,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -578,7 +581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -604,11 +607,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2053,6 +2066,7 @@
   <cols>
     <col min="1" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="20.21875" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2077,6 +2091,8 @@
       <c r="G1" s="9" t="s">
         <v>141</v>
       </c>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2088,7 +2104,7 @@
       <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="17">
         <v>1000</v>
       </c>
       <c r="E2" s="10">
@@ -2112,7 +2128,7 @@
       <c r="C3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="18">
         <v>80</v>
       </c>
       <c r="E3" s="11">
@@ -2144,7 +2160,7 @@
       <c r="C4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="17">
         <v>130</v>
       </c>
       <c r="E4" s="10">
@@ -2176,7 +2192,7 @@
       <c r="C5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="18">
         <v>900</v>
       </c>
       <c r="E5" s="11">
@@ -2208,7 +2224,7 @@
       <c r="C6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="17">
         <v>70</v>
       </c>
       <c r="E6" s="10">
@@ -2230,7 +2246,7 @@
       <c r="C7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="11">
         <v>45</v>
       </c>
@@ -2252,7 +2268,7 @@
       <c r="C8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="17">
         <v>30</v>
       </c>
       <c r="E8" s="10">
@@ -2276,7 +2292,7 @@
       <c r="C9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="18">
         <v>90</v>
       </c>
       <c r="E9" s="11">
@@ -2300,7 +2316,7 @@
       <c r="C10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="17">
         <v>500</v>
       </c>
       <c r="E10" s="10">
@@ -2324,7 +2340,7 @@
       <c r="C11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="18">
         <v>130</v>
       </c>
       <c r="E11" s="11">
@@ -2348,7 +2364,7 @@
       <c r="C12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="17">
         <v>950</v>
       </c>
       <c r="E12" s="10">
@@ -2372,7 +2388,7 @@
       <c r="C13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="18">
         <v>90</v>
       </c>
       <c r="E13" s="11">
@@ -2394,7 +2410,7 @@
       <c r="C14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="17">
         <v>120</v>
       </c>
       <c r="E14" s="10">
@@ -2416,7 +2432,7 @@
       <c r="C15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="18">
         <v>150</v>
       </c>
       <c r="E15" s="11">
@@ -2440,7 +2456,7 @@
       <c r="C16" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="17">
         <v>250</v>
       </c>
       <c r="E16" s="10">
@@ -2464,7 +2480,7 @@
       <c r="C17" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="18">
         <v>50</v>
       </c>
       <c r="E17" s="11">
@@ -2488,7 +2504,7 @@
       <c r="C18" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="17">
         <v>160</v>
       </c>
       <c r="E18" s="10">
@@ -2512,7 +2528,7 @@
       <c r="C19" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="18">
         <v>980</v>
       </c>
       <c r="E19" s="11">
@@ -2536,7 +2552,7 @@
       <c r="C20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="17">
         <v>150</v>
       </c>
       <c r="E20" s="10">
@@ -2560,7 +2576,7 @@
       <c r="C21" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="18"/>
       <c r="E21" s="11">
         <v>10</v>
       </c>
@@ -2582,7 +2598,7 @@
       <c r="C22" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="17">
         <v>700</v>
       </c>
       <c r="E22" s="10">
@@ -2606,7 +2622,7 @@
       <c r="C23" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="18">
         <v>80</v>
       </c>
       <c r="E23" s="11">
@@ -2630,7 +2646,7 @@
       <c r="C24" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="17">
         <v>150</v>
       </c>
       <c r="E24" s="10">
@@ -2652,7 +2668,7 @@
       <c r="C25" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="17">
         <v>800</v>
       </c>
       <c r="E25" s="10">
@@ -2676,7 +2692,7 @@
       <c r="C26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="18"/>
       <c r="E26" s="11">
         <v>25</v>
       </c>
@@ -2698,7 +2714,7 @@
       <c r="C27" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="17">
         <v>400</v>
       </c>
       <c r="E27" s="10">
@@ -2722,7 +2738,7 @@
       <c r="C28" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="17">
         <v>60</v>
       </c>
       <c r="E28" s="10">
@@ -2746,7 +2762,7 @@
       <c r="C29" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="18">
         <v>40</v>
       </c>
       <c r="E29" s="11">
@@ -2770,7 +2786,7 @@
       <c r="C30" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="17">
         <v>130</v>
       </c>
       <c r="E30" s="10">
@@ -2794,7 +2810,7 @@
       <c r="C31" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="18">
         <v>50</v>
       </c>
       <c r="E31" s="11">
@@ -2818,7 +2834,7 @@
       <c r="C32" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="18">
         <v>100</v>
       </c>
       <c r="E32" s="11">
@@ -3951,7 +3967,43 @@
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B50:C50"/>
   </mergeCells>
+  <conditionalFormatting sqref="D2:D32">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{96D8A347-61C8-41C3-9778-8AB57236F970}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F32">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>F2="Electronics"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{96D8A347-61C8-41C3-9778-8AB57236F970}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D2:D32</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/EXCEL/ASSIGNMENT_2.xlsx
+++ b/EXCEL/ASSIGNMENT_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EXCEL_NEW\ASSIGNMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB7ABF5-B595-4572-A84B-8EEF1A1C7704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D9B36D-7E56-40FA-8BE8-600C015AC31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="144">
   <si>
     <t>Perform the following in the dataset from the 'Dataset' sheet.</t>
   </si>
@@ -464,14 +464,21 @@
   </si>
   <si>
     <t>Product Brand</t>
+  </si>
+  <si>
+    <t>Manufacturing Date</t>
+  </si>
+  <si>
+    <t>Country Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -581,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -609,6 +616,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2066,7 +2077,7 @@
   <cols>
     <col min="1" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="20.21875" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2091,8 +2102,12 @@
       <c r="G1" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="H1" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2117,8 +2132,16 @@
         <f>_xlfn.CONCAT(B2," ",C2)</f>
         <v>Laptop Dell</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="20" t="str">
+        <f>LEFT(A2,6)</f>
+        <v>28-JAN</v>
+      </c>
+      <c r="I2" t="str">
+        <f>RIGHT(A2,2)</f>
+        <v>US</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>29</v>
       </c>
@@ -2141,7 +2164,14 @@
         <f t="shared" ref="G3:G32" si="0">_xlfn.CONCAT(B3," ",C3)</f>
         <v>Sneakers Nike</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="H3" s="20" t="str">
+        <f t="shared" ref="H3:H32" si="1">LEFT(A3,6)</f>
+        <v>15-FEB</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I32" si="2">RIGHT(A3,2)</f>
+        <v>US</v>
+      </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -2173,7 +2203,14 @@
         <f t="shared" si="0"/>
         <v>Coffee Maker Keurig</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="H4" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>03-MAR</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
       <c r="J4" s="7"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -2205,7 +2242,14 @@
         <f t="shared" si="0"/>
         <v>Smartphone Samsung</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="H5" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>11-APR</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -2235,6 +2279,14 @@
         <f t="shared" si="0"/>
         <v>Backpack North Face</v>
       </c>
+      <c r="H6" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>22-MAY</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
@@ -2257,6 +2309,14 @@
         <f t="shared" si="0"/>
         <v>Headphones Sony</v>
       </c>
+      <c r="H7" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>07-JUN</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
@@ -2281,6 +2341,14 @@
         <f t="shared" si="0"/>
         <v>T-shirt Adidas</v>
       </c>
+      <c r="H8" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>19-JUL</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -2305,6 +2373,14 @@
         <f t="shared" si="0"/>
         <v>Blender Ninja</v>
       </c>
+      <c r="H9" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>23-AUG</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
@@ -2329,6 +2405,14 @@
         <f t="shared" si="0"/>
         <v>Tablet Apple</v>
       </c>
+      <c r="H10" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>05-SEP</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
@@ -2353,6 +2437,14 @@
         <f t="shared" si="0"/>
         <v>Hiking Boots Timberland</v>
       </c>
+      <c r="H11" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>14-OCT</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
@@ -2376,6 +2468,14 @@
       <c r="G12" t="str">
         <f t="shared" si="0"/>
         <v>Laptop HP</v>
+      </c>
+      <c r="H12" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>17-JUN</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="2"/>
+        <v>IN</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2399,6 +2499,14 @@
         <f t="shared" si="0"/>
         <v>Sneakers Adidas</v>
       </c>
+      <c r="H13" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>25-NOV</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="2"/>
+        <v>AU</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -2421,6 +2529,14 @@
         <f t="shared" si="0"/>
         <v>Coffee Maker Nespresso</v>
       </c>
+      <c r="H14" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>08-DEC</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="2"/>
+        <v>DE</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
@@ -2445,6 +2561,14 @@
         <f t="shared" si="0"/>
         <v>Smartwatch Fitbit</v>
       </c>
+      <c r="H15" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>18-FEB</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
@@ -2469,8 +2593,16 @@
         <f t="shared" si="0"/>
         <v>Headphones Bose</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H16" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>16-APR</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="2"/>
+        <v>ES</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>71</v>
       </c>
@@ -2493,8 +2625,16 @@
         <f t="shared" si="0"/>
         <v>Laptop Bag Samsonite</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>21-AUG</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>75</v>
       </c>
@@ -2517,8 +2657,16 @@
         <f t="shared" si="0"/>
         <v>Smartwatch Huawei</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>20-AUG</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="2"/>
+        <v>CN</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>77</v>
       </c>
@@ -2541,8 +2689,16 @@
         <f t="shared" si="0"/>
         <v>Laptop Asus</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>27-JAN</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="2"/>
+        <v>IT</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>79</v>
       </c>
@@ -2565,8 +2721,16 @@
         <f t="shared" si="0"/>
         <v>Sunglasses Oakley</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>01-MAR</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>82</v>
       </c>
@@ -2587,8 +2751,16 @@
         <f t="shared" si="0"/>
         <v>Camping Tent Coleman</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H21" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>14-AUG</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>85</v>
       </c>
@@ -2611,8 +2783,16 @@
         <f t="shared" si="0"/>
         <v>Camera Nikon</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>14-MAY</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="2"/>
+        <v>RU</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>88</v>
       </c>
@@ -2635,8 +2815,16 @@
         <f t="shared" si="0"/>
         <v>Microwave Panasonic</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H23" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>09-JAN</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>91</v>
       </c>
@@ -2657,8 +2845,16 @@
         <f t="shared" si="0"/>
         <v>Fitness Tracker Xiaomi</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H24" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>19-JUL</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="2"/>
+        <v>BR</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>94</v>
       </c>
@@ -2681,8 +2877,16 @@
         <f t="shared" si="0"/>
         <v>Smartphone Google</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>29-SEP</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>97</v>
       </c>
@@ -2703,8 +2907,16 @@
         <f t="shared" si="0"/>
         <v>Sunglasses Ray-Ban</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H26" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>03-JUN</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>99</v>
       </c>
@@ -2727,8 +2939,16 @@
         <f t="shared" si="0"/>
         <v>Blender Vitamix</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>11-JUL</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>101</v>
       </c>
@@ -2751,8 +2971,16 @@
         <f t="shared" si="0"/>
         <v>Dress Zara</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>07-MAR</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>104</v>
       </c>
@@ -2775,8 +3003,16 @@
         <f t="shared" si="0"/>
         <v>Toaster Hamilton</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>13-APR</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>107</v>
       </c>
@@ -2799,8 +3035,16 @@
         <f t="shared" si="0"/>
         <v>Fitness Tracker Garmin</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>24-MAY</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>109</v>
       </c>
@@ -2823,8 +3067,16 @@
         <f t="shared" si="0"/>
         <v>Jeans Levi's</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>02-DEC</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>112</v>
       </c>
@@ -2847,56 +3099,66 @@
         <f t="shared" si="0"/>
         <v>Watch Casio</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>09-JUL</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="2"/>
+        <v>FR</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="20"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>115</v>
       </c>
       <c r="B39" s="14"/>
     </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>121</v>
       </c>
       <c r="C41" s="13"/>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="13" t="s">
         <v>118</v>
       </c>
       <c r="C42" s="13"/>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="13" t="s">
         <v>119</v>
       </c>
       <c r="C43" s="13"/>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="13" t="s">
         <v>120</v>
       </c>
       <c r="C44" s="13"/>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>123</v>
